--- a/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.5.xlsx
+++ b/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.5.xlsx
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>no_dangling_node</t>
+          <t>no_dangling_node (hydroobject-eindpunt is verbonden met beginpunt van een ander hydroobject)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">

--- a/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.5.xlsx
+++ b/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.5.xlsx
@@ -10,7 +10,7 @@
     <sheet name="ValidationRules_1.5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ValidationRules_1.5'!$A$1:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ValidationRules_1.5'!$A$1:$H$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Profiel moet intersecten met een waterlijn</t>
+          <t>De profiellijn moet intersecten met een waterlijn</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BOK bovenstrooms plausibel (-8m - maaiveld)</t>
+          <t>De binnenonderkant (BOK) bovenstrooms is plausibel (de hoogte ligt tussen -8 m en 325 m)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOK benedenstrooms plausibel (-8m - maaiveld)</t>
+          <t>De binnenonderkant (BOK) benedenstrooms is plausibel (de hoogte ligt tussen -8 m en 325 m)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BOK bovenstrooms onder maaiveld</t>
+          <t>De binnenonderkant (BOK) bovenstrooms ligt onder het maaiveld</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BOK benedenstrooms onder maaiveld</t>
+          <t>De binnenonderkant (BOK) benedenstrooms ligt onder het maaiveld</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lengte groter dan 1 m</t>
+          <t>De lengte is groter dan 1 m</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>vormkoker ISIN (Rond)</t>
+          <t>vormduikersifonhevel ISIN (Rond)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Het bodemverhang van een duiker moet liggen tussen -2 cm/m (omhoog) en 5 cm/m (omlaag)</t>
+          <t>Het bodemverhang van een duiker moet tussen -2 cm/m (omhoog) en 5 cm/m (omlaag) liggen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Een duikersifonhevel zal geen overlap met een andere duikersifonhevel hebben</t>
+          <t>Een duikersifonhevel mag geen overlap met een andere duikersifonhevel hebben</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>De BOK bovenstrooms mag slechts minimaal lager liggen dan de bovenstroomse bodemhoogte van het hydroobject</t>
+          <t>De binnenonderkant (BOK) bovenstrooms mag slechts minimaal lager liggen dan de bovenstroomse bodemhoogte van het hydroobject</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>De BOK benedenstrooms mag slechts minimaal lager liggen dan de bendenstroomse bodemhoogte van het hydroobject</t>
+          <t>De binnenonderkant (BOK) benedenstrooms mag slechts minimaal lager liggen dan de bendenstroomse bodemhoogte van het hydroobject</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>hoogstedoorstroomhoogte plausibel (-8m - 325m)</t>
+          <t>De hoogstedoorstroomhoogte is plausibel (ligt tussen -8 m en 325 m)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>laagstedoorstroomhoogte plausibel (-8m - 325m)</t>
+          <t>De laagstedoorstroomhoogte is plausibel (ligt tussen -8 m en 325 m)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Constructie hoogte plausibel (-8m - 325m)</t>
+          <t>De constructiehoogte is plausibel (ligt tussen -8 m en 325 m)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Constructie moet lager liggen dan omringend maaiveld</t>
+          <t>De constructie moet lager liggen dan het omringende maaiveld</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>De kruinbreedte moet groter dan 0.3 zijn</t>
+          <t>De kruinbreedte moet groter dan 0.3 m zijn</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Afstand tot as watergang moet kleiner zijn dan 1 meter</t>
+          <t>De afstand tot de as van de watergang moet kleiner zijn dan 1 m</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>kruinbreedte is groter of gelijk aan de doorstroombreedte</t>
+          <t>De kruinbreedte is groter of gelijk aan de doorstroombreedte</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>De hoogste doorstroomhoogte van de kunstwerkopening zal lager of gelijk zijn aan de constructiehoogte</t>
+          <t>De hoogste doorstroomhoogte van de kunstwerkopening moet lager of gelijk zijn aan de constructiehoogte</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Een stuw zal geen overlap met een andere stuw hebben</t>
+          <t>Een stuw mag geen overlap met een andere stuw hebben</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>general_001_kunstwerkopening_laagstedoorstroomhoogte</t>
+          <t>general_001_doorstroomopening_laagstedoorstroomhoogte</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Berekening van 'kunstwerkopening_laagstedoorstroomhoogte'</t>
+          <t>Berekening van 'doorstroomopening_laagstedoorstroomhoogte'</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>statistic=min, related_object=kunstwerkopening, related_parameter=laagstedoorstroomhoogte</t>
+          <t>statistic=min, related_object=doorstroomopening, related_parameter=laagstedoorstroomhoogte</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>algemene berekening</t>
+          <t>logische validatie</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>general_002_kunstwerkopening_laagstedoorstroombreedte</t>
+          <t>validate_000_hoogtebovenzijde_plausibel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Berekening van 'kunstwerkopening_laagstedoorstroombreedte'</t>
+          <t>hoogtebovenzijde plausibel (-8m - 325m)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kritisch</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>object_relation (aggregatiewaarde ophalen uit gerelateerde objecttabel)</t>
+          <t>BE (waarde ligt tussen de min- en max-waarde)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>statistic=sum, related_object=kunstwerkopening, related_parameter=laagstedoorstroombreedte</t>
+          <t>parameter=hoogtebovenzijde, min=-8, max=325, inclusive=False</t>
         </is>
       </c>
     </row>
@@ -2128,22 +2128,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>algemene berekening</t>
+          <t>logische validatie</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>general_003_kunstwerkopening_hoogstedoorstroombreedte</t>
+          <t>validate_001_hoogteonderzijde_plausibel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Berekening van 'kunstwerkopening_hoogstedoorstroombreedte'</t>
+          <t>hoogteonderzijde plausibel (-8m - 325m)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kritisch</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>object_relation (aggregatiewaarde ophalen uit gerelateerde objecttabel)</t>
+          <t>BE (waarde ligt tussen de min- en max-waarde)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>statistic=sum, related_object=kunstwerkopening, related_parameter=hoogstedoorstroombreedte</t>
+          <t>parameter=hoogteonderzijde, min=-8, max=325, inclusive=False</t>
         </is>
       </c>
     </row>
@@ -2175,17 +2175,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>validate_000_hoogtebovenzijde_plausibel</t>
+          <t>validate_002_lengte_plausibel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>hoogtebovenzijde plausibel (-8m - 325m)</t>
+          <t>lengte plausibel (1m - 30m)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>kritisch</t>
+          <t>niet-kritisch</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2200,14 +2200,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>parameter=hoogtebovenzijde, min=-8, max=325, inclusive=False</t>
+          <t>parameter=lengte, min=1, max=30, inclusive=False</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>brug</t>
+          <t>pomp</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>validate_001_hoogteonderzijde_plausibel</t>
+          <t>validate_000_capaciteit_gt_0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>hoogteonderzijde plausibel (-8m - 325m)</t>
+          <t>De capaciteit moet groter dan 0 zijn</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2237,39 +2237,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BE (waarde ligt tussen de min- en max-waarde)</t>
+          <t>GT (linkerwaarde is groter dan rechterwaarde)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>parameter=hoogteonderzijde, min=-8, max=325, inclusive=False</t>
+          <t>left=maximalecapaciteit, right=0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>brug</t>
+          <t>gemaal</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>logische validatie</t>
+          <t>algemene berekening</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>validate_002_lengte_plausibel</t>
+          <t>general_000_pomp_aantal_pompen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>lengte plausibel (1m - 30m)</t>
+          <t>Berekening van 'pomp_aantal_pompen'</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>niet-kritisch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2279,39 +2279,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BE (waarde ligt tussen de min- en max-waarde)</t>
+          <t>object_relation (aggregatiewaarde ophalen uit gerelateerde objecttabel)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>parameter=lengte, min=1, max=30, inclusive=False</t>
+          <t>statistic=count, related_object=pomp, fill_value=0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>brug</t>
+          <t>gemaal</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>logische validatie</t>
+          <t>algemene berekening</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>validate_003_laagstedoorstroombreedte_plausibel</t>
+          <t>general_001_pomp_capaciteit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Een brug moet een plausibele laagste doorstroombreedte hebben</t>
+          <t>Berekening van 'pomp_capaciteit'</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>kritisch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2321,19 +2321,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BE (waarde ligt tussen de min- en max-waarde)</t>
+          <t>object_relation (aggregatiewaarde ophalen uit gerelateerde objecttabel)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>parameter=kunstwerkopening_laagstedoorstroombreedte, min=1, max=50, inclusive=False</t>
+          <t>statistic=sum, related_object=pomp, related_parameter=maximalecapaciteit, fill_value=0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>brug</t>
+          <t>gemaal</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>validate_004_hoogstedoorstroombreedte_plausibel</t>
+          <t>validate_000_aantal_pompen_gt_0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Een brug moet een plausibele hoogste doorstroombreedte hebben</t>
+          <t>Het aantal pompen moet groter dan nul zijn</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2363,19 +2363,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BE (waarde ligt tussen de min- en max-waarde)</t>
+          <t>GT (linkerwaarde is groter dan rechterwaarde)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>parameter=kunstwerkopening_hoogstedoorstroombreedte, min=1, max=50, inclusive=False</t>
+          <t>left=pomp_aantal_pompen, right=0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pomp</t>
+          <t>gemaal</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>validate_000_capaciteit_gt_0</t>
+          <t>validate_001_capaciteit_gt_0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>De capaciteit groter dan 0</t>
+          <t>De totale capaciteit moet groter dan nul zijn</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>left=maximalecapaciteit, right=0</t>
+          <t>left=pomp_capaciteit, right=0</t>
         </is>
       </c>
     </row>
@@ -2422,22 +2422,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>algemene berekening</t>
+          <t>topologische validatie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>general_000_pomp_aantal_pompen</t>
+          <t>validate_002_geen_overlap</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Berekening van 'pomp_aantal_pompen'</t>
+          <t>Een gemaal mag geen overlap met een ander gemaal hebben</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kritisch</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2447,39 +2447,39 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>object_relation (aggregatiewaarde ophalen uit gerelateerde objecttabel)</t>
+          <t>not_overlapping</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>statistic=count, related_object=pomp, fill_value=0</t>
+          <t>tolerance=1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>gemaal</t>
+          <t>hydroobject</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>algemene berekening</t>
+          <t>topologische validatie</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>general_001_pomp_capaciteit</t>
+          <t>validate_000_lengte_gt_1m</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Berekening van 'pomp_capaciteit'</t>
+          <t>Het hydroobject heeft voldoende lengte voor modelverwerking (minimaal 1 m)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kritisch</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2489,34 +2489,34 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>object_relation (aggregatiewaarde ophalen uit gerelateerde objecttabel)</t>
+          <t>geometry_length</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>statistic=sum, related_object=pomp, related_parameter=maximalecapaciteit, fill_value=0</t>
+          <t>length=1, statistic=min</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>gemaal</t>
+          <t>hydroobject</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>logische validatie</t>
+          <t>topologische validatie</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>validate_000_aantal_pompen_gt_0</t>
+          <t>validate_001_goed_gesplitst</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Het aantal pompen is groter dan nul</t>
+          <t>Het hydroobject wordt gescheiden bij een samenkomst of opsplitsing</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2531,34 +2531,34 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GT (linkerwaarde is groter dan rechterwaarde)</t>
+          <t>splitted_at_junction</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>left=pomp_aantal_pompen, right=0</t>
+          <t>tolerance=0.01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gemaal</t>
+          <t>hydroobject</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>logische validatie</t>
+          <t>topologische validatie</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>validate_001_capaciteit_gt_0</t>
+          <t>validate_002_goede_kruising</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Totale capaciteit is groter dan nul</t>
+          <t>Hydroobjecten kruisen elkaar alleen in combinatie met een duikersifonhevel of aquaduct</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2573,19 +2573,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GT (linkerwaarde is groter dan rechterwaarde)</t>
+          <t>structures_at_intersections</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>left=pomp_capaciteit, right=0</t>
+          <t>tolerance=0.01, structures=duikersifonhevel</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gemaal</t>
+          <t>hydroobject</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>validate_002_geen_overlap</t>
+          <t>validate_003_geen_eindpunt</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Een gemaal zal geen overlap met een ander gemaal hebben</t>
+          <t>Hydroobjecten sluiten aan elkaar aan en vormen een consistent geheel, er zijn geen "doodlopende" routes</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>not_overlapping</t>
+          <t>no_dangling_node (hydroobject-eindpunt is verbonden met beginpunt van een ander hydroobject)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>tolerance=1</t>
+          <t>tolerance=0.01</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>validate_000_lengte_gt_1m</t>
+          <t>validate_004_kunstwerk_op_grens_peilgebiedpraktijk</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hydroobject heeft voldoende lengte voor modelverwerking</t>
+          <t>Waar een hydroobject een grens van een peilgebiedpraktijk doorkruist, moet een peilscheidend kunstwerk liggen</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>geometry_length</t>
+          <t>structures_at_boundaries</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>length=1, statistic=min</t>
+          <t>areas=peilgebiedpraktijk, structures=gemaal, stuw, duikersifonhevel, tolerance=0.01, distance=25</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>validate_001_goed_gesplitst</t>
+          <t>validate_005_kunstwerk_tussen_hobject</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Een hydroobject wordt gescheiden bij een samenkomst of opsplitsing</t>
+          <t>Een stuw, gemaal of bodemval moet een hydroobject opsplitsen</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>splitted_at_junction</t>
+          <t>structures_at_nodes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>tolerance=0.01</t>
+          <t>structures=gemaal, stuw, bodemval, tolerance=1</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>validate_002_goede_kruising</t>
+          <t>validate_006_kunstwerk_op_grens_peilafwijkinggebied</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hydroobject kruist zichzelf alleen in combinatie met een duikersifonhevel of aquaduct</t>
+          <t>Waar een hydroobject een grens van een peilafwijkinggebied doorkruist, moet een peilscheidend kunstwerk liggen</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2741,39 +2741,39 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>structures_at_intersections</t>
+          <t>structures_at_boundaries</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>tolerance=0.01, structures=duikersifonhevel</t>
+          <t>areas=peilafwijkinggebied, structures=gemaal, stuw, duikersifonhevel, tolerance=0.01, distance=25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hydroobject</t>
+          <t>sturing</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>topologische validatie</t>
+          <t>algemene berekening</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>validate_003_geen_eindpunt</t>
+          <t>general_000_pomp_pompcapaciteit_m3min</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Hydroobject vormt een consistent geheel, er zijn geen "doodlopende" routes</t>
+          <t>Berekening van 'pomp_pompcapaciteit_m3min'</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>kritisch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2783,39 +2783,39 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>no_dangling_node (hydroobject-eindpunt is verbonden met beginpunt van een ander hydroobject)</t>
+          <t>join_parameter (koppeling met parameter uit ander objecttabel)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>tolerance=0.01</t>
+          <t>join_object=pomp, join_parameter=maximalecapaciteit, fill_value=0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hydroobject</t>
+          <t>sturing</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>topologische validatie</t>
+          <t>algemene berekening</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>validate_004_kunstwerk_op_grens_peilgebiedpraktijk</t>
+          <t>general_001_pomp_pompcapaciteit_m3s</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Waar een hydroobject een grens van een peilgebiedpraktijk doorkruist, moet een peilscheidend kunstwerk liggen</t>
+          <t>Berekening van 'pomp_pompcapaciteit_m3s'</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>kritisch</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2825,34 +2825,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>structures_at_boundaries</t>
+          <t>divide (quotiënt van linker- en rechterwaarde)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>areas=peilgebiedpraktijk, structures=gemaal, stuw, duikersifonhevel, tolerance=0.01, distance=25</t>
+          <t>left=pomp_pompcapaciteit_m3min, right=60</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hydroobject</t>
+          <t>sturing</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>topologische validatie</t>
+          <t>logische validatie</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>validate_005_kunstwerk_tussen_hobject</t>
+          <t>validate_000_periode_consistent</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Een stuw, gemaal of bodemval moet een hydroobject opsplitsen</t>
+          <t>Er mogen geen overlappende of ontbrekende periodes zitten van meerdere sturingen met dezelfde prioriteit per gestuurd object</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2867,34 +2867,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>structures_at_nodes</t>
+          <t>consistent_period</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>structures=gemaal, stuw, bodemval, tolerance=1</t>
+          <t>max_gap=1, groupers=pompid, afsluitmiddelid</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hydroobject</t>
+          <t>sturing</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>topologische validatie</t>
+          <t>logische validatie</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>validate_006_kunstwerk_op_grens_peilafwijkinggebied</t>
+          <t>validate_001_pomp_bestaat</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Waar een hydroobject een grens van een peilafwijkinggebied doorkruist, moet een peilscheidend kunstwerk liggen</t>
+          <t>De gestuurde pomp moet bestaan</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2904,17 +2904,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>pompid NOTNA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>structures_at_boundaries</t>
+          <t>join_object_exists (object komt voor in de gerelateerde objecttabel)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>areas=peilafwijkinggebied, structures=gemaal, stuw, duikersifonhevel, tolerance=0.01, distance=25</t>
+          <t>join_object=pomp</t>
         </is>
       </c>
     </row>
@@ -2926,37 +2926,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>algemene berekening</t>
+          <t>logische validatie</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>general_000_pomp_pompcapaciteit_m3min</t>
+          <t>validate_003_hydrologische_rvw_bestaat</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Berekening van 'pomp_pompcapaciteit_m3min'</t>
+          <t>De gestuurde hydrologische randvoorwaarde moet bestaan</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kritisch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>hydrologischerandvoorwaardeid NOTNA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>join_parameter (koppeling met parameter uit ander objecttabel)</t>
+          <t>join_object_exists (object komt voor in de gerelateerde objecttabel)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>join_object=pomp, join_parameter=maximalecapaciteit, fill_value=0</t>
+          <t>join_object=hydrologischerandvoorwaarde</t>
         </is>
       </c>
     </row>
@@ -2968,37 +2968,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>algemene berekening</t>
+          <t>logische validatie</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>general_001_pomp_pompcapaciteit_m3s</t>
+          <t>validate_004_vastewaarde_pmp_binnen_bereik</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Berekening van 'pomp_pompcapaciteit_m3s'</t>
+          <t>De vaste waarde pomp moet binnen het fysieke bereik van de stuurvariabele passen</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kritisch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>typestuurvariabele ISIN (pompdebiet)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>divide (quotiënt van linker- en rechterwaarde)</t>
+          <t>LE (linkerwaarde is minder dan of gelijk aan rechterwaarde)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>left=pomp_pompcapaciteit_m3min, right=60</t>
+          <t>left=vastewaarde, right=pomp_pompcapaciteit_m3s</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>validate_000_periode_consistent</t>
+          <t>validate_007_pmp_juiste_stuurvariabele</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Er mag geen overlap of gat in de periode zitten van meerdere sturingen met dezelfde prioriteit per gestuurd object</t>
+          <t>De gestuurde pomp moet de juiste stuurvariabele hebben</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3030,190 +3030,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>pompid NOTNA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>consistent_period</t>
+          <t>ISIN (waarde komt voor in lijst)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>max_gap=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>sturing</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>logische validatie</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>validate_001_pomp_bestaat</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>de gestuurde pomp moet bestaan</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>kritisch</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>pompid NOTNA</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>join_object_exists (object komt voor in de gerelateerde objecttabel)</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>join_object=pomp</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>sturing</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>logische validatie</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>validate_003_hydrologische_rvw_bestaat</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>de gestuurde hydrologische randvoorwaarde moet bestaan</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>kritisch</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>hydrologischerandvoorwaardeid NOTNA</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>join_object_exists (object komt voor in de gerelateerde objecttabel)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>join_object=hydrologischerandvoorwaarde</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>sturing</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>logische validatie</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>validate_004_vastewaarde_pmp_binnen_bereik</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>vaste waarde pomp zal binnen het fysieke bereik van de stuurvariabele passen</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>kritisch</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>stuurvariabele ISIN (pompdebiet)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>LE (linkerwaarde is minder dan of gelijk aan rechterwaarde)</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>left=vastewaarde, right=pomp_pompcapaciteit_m3s</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>sturing</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>logische validatie</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>validate_007_pmp_juiste_stuurvariabele</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>gestuurde pomp heeft juiste stuurvariabele</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>kritisch</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>pompid NOTNA</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>ISIN (waarde komt voor in lijst)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>parameter=stuurvariabele, array=pompdebiet</t>
+          <t>parameter=typestuurvariabele, array=pompdebiet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:H62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>